--- a/Assets/ArtRes/Excel/角色属性表.xlsx
+++ b/Assets/ArtRes/Excel/角色属性表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_Project\weiqi4\Assets\ArtRes\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199DAD72-D6E0-47E3-9695-6178FAAA24ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T_Role" sheetId="1" r:id="rId1"/>
@@ -14,12 +20,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>36593</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -36,7 +42,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>ID_</t>
         </r>
@@ -57,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="279">
   <si>
     <t>f_id</t>
   </si>
@@ -161,9 +167,6 @@
     <t>职业</t>
   </si>
   <si>
-    <t>技能类型</t>
-  </si>
-  <si>
     <t>移动力</t>
   </si>
   <si>
@@ -876,19 +879,41 @@
   </si>
   <si>
     <t>圣裁之怒</t>
+  </si>
+  <si>
+    <t>耄耋</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>dead</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fall</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>耄耋哈气</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>5_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellow</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>圆头耄耋</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -910,150 +935,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1063,10 +944,24 @@
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1075,7 +970,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1097,188 +992,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1312,251 +1027,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1590,13 +1063,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1605,75 +1078,33 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1931,32 +1362,32 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:W68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="9.66666666666667" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10.5" style="4" customWidth="1"/>
     <col min="8" max="8" width="11.5" style="4" customWidth="1"/>
     <col min="9" max="9" width="9" style="4"/>
     <col min="10" max="10" width="11.5" style="4" customWidth="1"/>
     <col min="14" max="14" width="9.75" customWidth="1"/>
-    <col min="15" max="15" width="9.91666666666667" customWidth="1"/>
-    <col min="16" max="16" width="9.41666666666667" style="4" customWidth="1"/>
+    <col min="15" max="15" width="9.9140625" customWidth="1"/>
+    <col min="16" max="16" width="9.4140625" style="4" customWidth="1"/>
     <col min="17" max="17" width="9.25" style="4" customWidth="1"/>
-    <col min="18" max="18" width="11.4166666666667" style="4" customWidth="1"/>
+    <col min="18" max="18" width="11.4140625" style="4" customWidth="1"/>
     <col min="19" max="19" width="36.25" customWidth="1"/>
-    <col min="20" max="20" width="27.6666666666667" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="38.15" customHeight="1" spans="1:23">
+    <row r="1" spans="1:23" s="1" customFormat="1" ht="38.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2008,7 +1439,7 @@
       <c r="Q1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="16" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -2027,7 +1458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:23">
+    <row r="2" spans="1:23" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -2053,7 +1484,7 @@
       <c r="O2" s="15"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
-      <c r="R2" s="18"/>
+      <c r="R2" s="16"/>
       <c r="S2" s="1" t="s">
         <v>23</v>
       </c>
@@ -2070,12 +1501,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="38.15" customHeight="1" spans="1:22">
+    <row r="4" spans="1:23" s="2" customFormat="1" ht="38.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>27</v>
       </c>
@@ -2097,64 +1528,64 @@
       <c r="G4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="10">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="K4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="L4" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="M4" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="N4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="O4" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="P4" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="14" t="s">
+      <c r="Q4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="14" t="s">
+      <c r="R4" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="19" t="s">
+      <c r="S4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="V4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A5" s="11" t="s">
+      <c r="B5" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="C5" s="12">
         <v>0</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="12">
         <v>10</v>
@@ -2191,33 +1622,33 @@
         <v>1</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T5" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="T5" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="U5" s="11" t="s">
+      <c r="V5" t="s">
         <v>53</v>
       </c>
-      <c r="V5" s="16" t="s">
+      <c r="W5" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="W5" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A6" s="11" t="s">
+      <c r="B6" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="12">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" s="12">
-        <v>1</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>57</v>
       </c>
       <c r="E6" s="12">
         <v>25</v>
@@ -2235,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="12">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K6" s="12">
         <v>55</v>
@@ -2254,33 +1685,33 @@
         <v>1</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T6" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T6" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U6" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" t="s">
+        <v>53</v>
+      </c>
+      <c r="W6" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="V6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W6" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A7" s="11" t="s">
+      <c r="B7" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>60</v>
       </c>
       <c r="C7" s="12">
         <v>2</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="12">
         <v>80</v>
@@ -2317,33 +1748,33 @@
         <v>1</v>
       </c>
       <c r="S7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T7" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T7" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U7" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="V7" t="s">
+        <v>53</v>
+      </c>
+      <c r="W7" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="V7" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W7" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A8" s="11" t="s">
+      <c r="B8" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>63</v>
       </c>
       <c r="C8" s="12">
         <v>3</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="12">
         <v>200</v>
@@ -2380,33 +1811,33 @@
         <v>1</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T8" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T8" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U8" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="V8" t="s">
+        <v>53</v>
+      </c>
+      <c r="W8" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="V8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W8" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A9" s="11" t="s">
+      <c r="B9" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="C9" s="12">
         <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="12">
         <v>700</v>
@@ -2443,33 +1874,33 @@
         <v>1</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T9" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T9" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U9" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="V9" t="s">
+        <v>53</v>
+      </c>
+      <c r="W9" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="V9" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W9" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A10" s="11" t="s">
+      <c r="B10" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>70</v>
       </c>
       <c r="C10" s="12">
         <v>5</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="12">
         <v>1500</v>
@@ -2506,33 +1937,33 @@
         <v>1</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T10" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T10" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U10" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="V10" t="s">
+        <v>53</v>
+      </c>
+      <c r="W10" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="V10" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W10" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A11" s="11" t="s">
+      <c r="B11" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>73</v>
       </c>
       <c r="C11" s="12">
         <v>6</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="12">
         <v>4000</v>
@@ -2569,33 +2000,33 @@
         <v>1</v>
       </c>
       <c r="S11" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T11" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T11" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U11" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="V11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W11" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="V11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W11" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A12" s="11" t="s">
+      <c r="B12" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="C12" s="12">
         <v>7</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" s="12">
         <v>10000</v>
@@ -2632,33 +2063,33 @@
         <v>1</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T12" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T12" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="V12" t="s">
+        <v>53</v>
+      </c>
+      <c r="W12" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="V12" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W12" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A13" s="11" t="s">
+      <c r="B13" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="12">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="C13" s="12">
-        <v>1</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="E13" s="12">
         <v>30</v>
@@ -2695,33 +2126,33 @@
         <v>1</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T13" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T13" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U13" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="V13" t="s">
+        <v>53</v>
+      </c>
+      <c r="W13" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="V13" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W13" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A14" s="11" t="s">
+      <c r="B14" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>84</v>
       </c>
       <c r="C14" s="12">
         <v>2</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" s="12">
         <v>96</v>
@@ -2758,33 +2189,33 @@
         <v>1</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T14" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T14" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="V14" t="s">
+        <v>53</v>
+      </c>
+      <c r="W14" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="V14" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W14" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A15" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="C15" s="12">
         <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" s="12">
         <v>240</v>
@@ -2821,33 +2252,33 @@
         <v>1</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T15" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U15" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="V15" t="s">
+        <v>53</v>
+      </c>
+      <c r="W15" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="V15" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W15" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A16" s="11" t="s">
+      <c r="B16" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="C16" s="12">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="12">
         <v>840</v>
@@ -2884,33 +2315,33 @@
         <v>1</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T16" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T16" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U16" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="V16" t="s">
+        <v>53</v>
+      </c>
+      <c r="W16" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="V16" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W16" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A17" s="11" t="s">
+      <c r="B17" s="11" t="s">
         <v>93</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>94</v>
       </c>
       <c r="C17" s="12">
         <v>5</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="12">
         <v>1800</v>
@@ -2947,33 +2378,33 @@
         <v>1</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T17" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T17" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U17" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="V17" t="s">
+        <v>53</v>
+      </c>
+      <c r="W17" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="V17" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W17" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A18" s="11" t="s">
+      <c r="B18" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="C18" s="12">
         <v>6</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18" s="12">
         <v>5600</v>
@@ -2991,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="12">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K18" s="12">
         <v>205</v>
@@ -3010,33 +2441,33 @@
         <v>1</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T18" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T18" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U18" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="V18" t="s">
+        <v>53</v>
+      </c>
+      <c r="W18" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="V18" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W18" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A19" s="11" t="s">
+      <c r="B19" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="C19" s="12">
         <v>7</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="12">
         <v>12000</v>
@@ -3073,33 +2504,33 @@
         <v>1</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T19" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T19" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U19" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="V19" t="s">
+        <v>53</v>
+      </c>
+      <c r="W19" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="V19" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W19" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A20" s="11" t="s">
+      <c r="B20" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>104</v>
-      </c>
-      <c r="C20" s="12">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>105</v>
       </c>
       <c r="E20" s="12">
         <v>36</v>
@@ -3136,33 +2567,33 @@
         <v>1</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T20" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T20" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U20" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="V20" t="s">
+        <v>53</v>
+      </c>
+      <c r="W20" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="V20" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W20" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A21" s="11" t="s">
+      <c r="B21" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="C21" s="12">
         <v>2</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" s="12">
         <v>115</v>
@@ -3199,33 +2630,33 @@
         <v>1</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T21" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T21" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U21" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="V21" t="s">
+        <v>53</v>
+      </c>
+      <c r="W21" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="V21" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W21" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A22" s="11" t="s">
+      <c r="B22" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="C22" s="12">
         <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22" s="12">
         <v>255</v>
@@ -3262,33 +2693,33 @@
         <v>1</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T22" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T22" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U22" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="V22" t="s">
+        <v>53</v>
+      </c>
+      <c r="W22" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="V22" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W22" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A23" s="11" t="s">
+      <c r="B23" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="C23" s="12">
         <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E23" s="12">
         <v>1000</v>
@@ -3325,33 +2756,33 @@
         <v>1</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T23" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T23" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U23" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="V23" t="s">
+        <v>53</v>
+      </c>
+      <c r="W23" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="V23" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W23" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A24" s="11" t="s">
+      <c r="B24" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="C24" s="12">
         <v>5</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="12">
         <v>2160</v>
@@ -3388,33 +2819,33 @@
         <v>1</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T24" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T24" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U24" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="V24" t="s">
+        <v>53</v>
+      </c>
+      <c r="W24" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="V24" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W24" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A25" s="11" t="s">
+      <c r="B25" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="C25" s="12">
         <v>6</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E25" s="12">
         <v>6720</v>
@@ -3432,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="12">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K25" s="12">
         <v>155</v>
@@ -3451,33 +2882,33 @@
         <v>1</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T25" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T25" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U25" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="V25" t="s">
+        <v>53</v>
+      </c>
+      <c r="W25" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="V25" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W25" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A26" s="11" t="s">
+      <c r="B26" s="11" t="s">
         <v>123</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>124</v>
       </c>
       <c r="C26" s="12">
         <v>7</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E26" s="12">
         <v>14400</v>
@@ -3514,33 +2945,33 @@
         <v>1</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T26" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T26" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V26" t="s">
+        <v>53</v>
+      </c>
+      <c r="W26" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="V26" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W26" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A27" s="11" t="s">
+      <c r="B27" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="C27" s="12">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="C27" s="12">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="E27" s="12">
         <v>45</v>
@@ -3577,33 +3008,33 @@
         <v>1</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T27" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T27" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U27" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="V27" t="s">
+        <v>53</v>
+      </c>
+      <c r="W27" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="V27" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W27" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A28" s="11" t="s">
+      <c r="B28" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>132</v>
       </c>
       <c r="C28" s="12">
         <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E28" s="12">
         <v>136</v>
@@ -3640,33 +3071,33 @@
         <v>1</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T28" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T28" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U28" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="V28" t="s">
+        <v>53</v>
+      </c>
+      <c r="W28" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="V28" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W28" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A29" s="11" t="s">
+      <c r="B29" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="C29" s="12">
         <v>3</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E29" s="12">
         <v>305</v>
@@ -3703,33 +3134,33 @@
         <v>1</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T29" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T29" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U29" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="V29" t="s">
+        <v>53</v>
+      </c>
+      <c r="W29" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="V29" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W29" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A30" s="11" t="s">
+      <c r="B30" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>138</v>
       </c>
       <c r="C30" s="12">
         <v>4</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E30" s="12">
         <v>1200</v>
@@ -3747,7 +3178,7 @@
         <v>2</v>
       </c>
       <c r="J30" s="12">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K30" s="12">
         <v>145</v>
@@ -3766,33 +3197,33 @@
         <v>1</v>
       </c>
       <c r="S30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T30" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T30" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U30" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="V30" t="s">
+        <v>53</v>
+      </c>
+      <c r="W30" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="V30" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W30" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A31" s="11" t="s">
+      <c r="B31" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="C31" s="12">
         <v>5</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E31" s="12">
         <v>2600</v>
@@ -3829,33 +3260,33 @@
         <v>1</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T31" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T31" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U31" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="V31" t="s">
+        <v>53</v>
+      </c>
+      <c r="W31" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="V31" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W31" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A32" s="11" t="s">
+      <c r="B32" s="11" t="s">
         <v>144</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>145</v>
       </c>
       <c r="C32" s="12">
         <v>6</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E32" s="12">
         <v>8000</v>
@@ -3892,33 +3323,33 @@
         <v>1</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T32" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T32" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U32" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="V32" t="s">
+        <v>53</v>
+      </c>
+      <c r="W32" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="V32" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W32" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A33" s="11" t="s">
+      <c r="B33" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>148</v>
       </c>
       <c r="C33" s="12">
         <v>7</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E33" s="12">
         <v>17280</v>
@@ -3955,33 +3386,33 @@
         <v>1</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T33" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T33" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U33" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="V33" t="s">
+        <v>53</v>
+      </c>
+      <c r="W33" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="V33" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W33" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A34" s="11" t="s">
+      <c r="B34" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="C34" s="12">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13" t="s">
         <v>152</v>
-      </c>
-      <c r="C34" s="12">
-        <v>1</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>153</v>
       </c>
       <c r="E34" s="12">
         <v>55</v>
@@ -4018,33 +3449,33 @@
         <v>2</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T34" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T34" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U34" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="V34" t="s">
+        <v>53</v>
+      </c>
+      <c r="W34" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="V34" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W34" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A35" s="11" t="s">
+      <c r="B35" s="11" t="s">
         <v>155</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>156</v>
       </c>
       <c r="C35" s="12">
         <v>2</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E35" s="12">
         <v>160</v>
@@ -4081,33 +3512,33 @@
         <v>2</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T35" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T35" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U35" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="V35" t="s">
+        <v>53</v>
+      </c>
+      <c r="W35" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="V35" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W35" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A36" s="11" t="s">
+      <c r="B36" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>159</v>
       </c>
       <c r="C36" s="12">
         <v>3</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E36" s="12">
         <v>360</v>
@@ -4144,33 +3575,33 @@
         <v>3</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T36" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T36" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U36" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="V36" t="s">
+        <v>53</v>
+      </c>
+      <c r="W36" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="V36" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W36" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A37" s="11" t="s">
+      <c r="B37" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="C37" s="12">
         <v>4</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37" s="12">
         <v>1440</v>
@@ -4207,33 +3638,33 @@
         <v>3</v>
       </c>
       <c r="S37" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T37" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T37" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U37" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="V37" t="s">
+        <v>53</v>
+      </c>
+      <c r="W37" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="V37" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W37" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A38" s="11" t="s">
+      <c r="B38" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="C38" s="12">
         <v>5</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38" s="12">
         <v>3120</v>
@@ -4270,33 +3701,33 @@
         <v>4</v>
       </c>
       <c r="S38" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T38" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T38" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U38" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="V38" t="s">
+        <v>53</v>
+      </c>
+      <c r="W38" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="V38" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W38" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A39" s="11" t="s">
+      <c r="B39" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="C39" s="12">
         <v>6</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E39" s="12">
         <v>9600</v>
@@ -4314,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="12">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K39" s="12">
         <v>195</v>
@@ -4333,33 +3764,33 @@
         <v>4</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T39" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T39" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U39" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="V39" t="s">
+        <v>53</v>
+      </c>
+      <c r="W39" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="V39" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W39" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A40" s="11" t="s">
+      <c r="B40" s="11" t="s">
         <v>171</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>172</v>
       </c>
       <c r="C40" s="12">
         <v>7</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E40" s="12">
         <v>20800</v>
@@ -4396,33 +3827,33 @@
         <v>5</v>
       </c>
       <c r="S40" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T40" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T40" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U40" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="V40" t="s">
+        <v>53</v>
+      </c>
+      <c r="W40" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="V40" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W40" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A41" s="11" t="s">
+      <c r="B41" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="C41" s="12">
+        <v>1</v>
+      </c>
+      <c r="D41" s="13" t="s">
         <v>176</v>
-      </c>
-      <c r="C41" s="12">
-        <v>1</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>177</v>
       </c>
       <c r="E41" s="12">
         <v>66</v>
@@ -4459,33 +3890,33 @@
         <v>2</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T41" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T41" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U41" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="V41" t="s">
+        <v>53</v>
+      </c>
+      <c r="W41" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="V41" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W41" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A42" s="11" t="s">
+      <c r="B42" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>180</v>
       </c>
       <c r="C42" s="12">
         <v>2</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E42" s="12">
         <v>192</v>
@@ -4522,33 +3953,33 @@
         <v>2</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T42" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T42" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U42" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="V42" t="s">
+        <v>53</v>
+      </c>
+      <c r="W42" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="V42" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W42" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A43" s="11" t="s">
+      <c r="B43" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="C43" s="12">
         <v>3</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E43" s="12">
         <v>432</v>
@@ -4585,33 +4016,33 @@
         <v>2</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T43" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T43" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U43" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="V43" t="s">
+        <v>53</v>
+      </c>
+      <c r="W43" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="V43" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W43" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A44" s="11" t="s">
+      <c r="B44" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="C44" s="12">
         <v>4</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E44" s="12">
         <v>1728</v>
@@ -4629,7 +4060,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="12">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K44" s="12">
         <v>80</v>
@@ -4648,33 +4079,33 @@
         <v>3</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T44" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T44" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U44" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="V44" t="s">
+        <v>53</v>
+      </c>
+      <c r="W44" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="V44" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W44" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A45" s="11" t="s">
+      <c r="B45" s="11" t="s">
         <v>189</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>190</v>
       </c>
       <c r="C45" s="12">
         <v>5</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E45" s="12">
         <v>3744</v>
@@ -4711,33 +4142,33 @@
         <v>3</v>
       </c>
       <c r="S45" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T45" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T45" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U45" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="V45" t="s">
+        <v>53</v>
+      </c>
+      <c r="W45" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="V45" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W45" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A46" s="11" t="s">
+      <c r="B46" s="11" t="s">
         <v>192</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>193</v>
       </c>
       <c r="C46" s="12">
         <v>6</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E46" s="12">
         <v>11520</v>
@@ -4774,33 +4205,33 @@
         <v>3</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T46" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T46" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U46" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="V46" t="s">
+        <v>53</v>
+      </c>
+      <c r="W46" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="V46" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W46" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A47" s="11" t="s">
+      <c r="B47" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>196</v>
       </c>
       <c r="C47" s="12">
         <v>7</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E47" s="12">
         <v>24960</v>
@@ -4837,33 +4268,33 @@
         <v>4</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T47" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T47" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U47" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="V47" t="s">
+        <v>53</v>
+      </c>
+      <c r="W47" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="V47" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W47" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A48" s="11" t="s">
+      <c r="B48" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="C48" s="12">
+        <v>1</v>
+      </c>
+      <c r="D48" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="C48" s="12">
-        <v>1</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>201</v>
       </c>
       <c r="E48" s="12">
         <v>85</v>
@@ -4900,33 +4331,33 @@
         <v>2</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T48" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T48" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U48" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="V48" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="V48" s="11" t="s">
+      <c r="W48" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="W48" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A49" s="11" t="s">
+      <c r="B49" s="11" t="s">
         <v>204</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>205</v>
       </c>
       <c r="C49" s="12">
         <v>2</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E49" s="12">
         <v>230</v>
@@ -4963,33 +4394,33 @@
         <v>2</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T49" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T49" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U49" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="V49" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="W49" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="V49" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="W49" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A50" s="11" t="s">
+      <c r="B50" s="11" t="s">
         <v>207</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>208</v>
       </c>
       <c r="C50" s="12">
         <v>3</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E50" s="12">
         <v>518</v>
@@ -5026,33 +4457,33 @@
         <v>2</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T50" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T50" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U50" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="V50" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="W50" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="V50" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="W50" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A51" s="11" t="s">
+      <c r="B51" s="11" t="s">
         <v>210</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>211</v>
       </c>
       <c r="C51" s="12">
         <v>4</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E51" s="12">
         <v>2074</v>
@@ -5089,33 +4520,33 @@
         <v>3</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T51" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T51" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U51" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="V51" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="W51" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="V51" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="W51" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A52" s="11" t="s">
+      <c r="B52" s="11" t="s">
         <v>214</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>215</v>
       </c>
       <c r="C52" s="12">
         <v>5</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E52" s="12">
         <v>4493</v>
@@ -5152,33 +4583,33 @@
         <v>3</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T52" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T52" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U52" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="V52" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="W52" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="V52" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="W52" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A53" s="11" t="s">
+      <c r="B53" s="11" t="s">
         <v>217</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="C53" s="12">
         <v>6</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E53" s="12">
         <v>13824</v>
@@ -5215,33 +4646,33 @@
         <v>3</v>
       </c>
       <c r="S53" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T53" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T53" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U53" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="V53" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="W53" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="V53" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="W53" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A54" s="11" t="s">
+      <c r="B54" s="11" t="s">
         <v>220</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>221</v>
       </c>
       <c r="C54" s="12">
         <v>7</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E54" s="12">
         <v>29952</v>
@@ -5278,33 +4709,33 @@
         <v>4</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T54" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T54" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U54" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="V54" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="W54" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="V54" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="W54" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A55" s="11" t="s">
+      <c r="B55" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="C55" s="12">
+        <v>1</v>
+      </c>
+      <c r="D55" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="C55" s="12">
-        <v>1</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>226</v>
       </c>
       <c r="E55" s="12">
         <v>102</v>
@@ -5341,33 +4772,33 @@
         <v>2</v>
       </c>
       <c r="S55" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T55" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T55" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U55" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="V55" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="V55" s="11" t="s">
+      <c r="W55" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="W55" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A56" s="11" t="s">
+      <c r="B56" s="11" t="s">
         <v>229</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>230</v>
       </c>
       <c r="C56" s="12">
         <v>2</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E56" s="12">
         <v>276</v>
@@ -5385,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="12">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K56" s="12">
         <v>105</v>
@@ -5404,33 +4835,33 @@
         <v>2</v>
       </c>
       <c r="S56" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T56" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T56" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U56" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="V56" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="W56" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="V56" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="W56" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A57" s="11" t="s">
+      <c r="B57" s="11" t="s">
         <v>232</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>233</v>
       </c>
       <c r="C57" s="12">
         <v>3</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E57" s="12">
         <v>622</v>
@@ -5467,33 +4898,33 @@
         <v>3</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T57" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T57" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U57" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="V57" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="W57" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="V57" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="W57" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A58" s="11" t="s">
+      <c r="B58" s="11" t="s">
         <v>235</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>236</v>
       </c>
       <c r="C58" s="12">
         <v>4</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E58" s="12">
         <v>2489</v>
@@ -5530,33 +4961,33 @@
         <v>3</v>
       </c>
       <c r="S58" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T58" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T58" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U58" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="V58" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="W58" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="V58" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="W58" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A59" s="11" t="s">
+      <c r="B59" s="11" t="s">
         <v>239</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>240</v>
       </c>
       <c r="C59" s="12">
         <v>5</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E59" s="12">
         <v>5392</v>
@@ -5593,33 +5024,33 @@
         <v>4</v>
       </c>
       <c r="S59" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T59" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T59" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U59" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="V59" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="W59" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="V59" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="W59" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A60" s="11" t="s">
+      <c r="B60" s="11" t="s">
         <v>242</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="C60" s="12">
         <v>6</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E60" s="12">
         <v>16589</v>
@@ -5637,7 +5068,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="12">
-        <v>0.700000000000001</v>
+        <v>0.70000000000000095</v>
       </c>
       <c r="K60" s="12">
         <v>205</v>
@@ -5656,33 +5087,33 @@
         <v>4</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T60" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T60" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U60" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="V60" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="W60" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="V60" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="W60" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" s="3" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A61" s="11" t="s">
+      <c r="B61" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>246</v>
       </c>
       <c r="C61" s="12">
         <v>7</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E61" s="12">
         <v>35942</v>
@@ -5700,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="J61" s="12">
-        <v>0.600000000000001</v>
+        <v>0.60000000000000098</v>
       </c>
       <c r="K61" s="12">
         <v>230</v>
@@ -5719,33 +5150,33 @@
         <v>5</v>
       </c>
       <c r="S61" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T61" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T61" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U61" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="V61" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="W61" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="V61" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="W61" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23">
-      <c r="A62" s="11" t="s">
+      <c r="B62" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="C62" s="12">
+        <v>1</v>
+      </c>
+      <c r="D62" s="13" t="s">
         <v>250</v>
-      </c>
-      <c r="C62" s="12">
-        <v>1</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>251</v>
       </c>
       <c r="E62" s="12">
         <v>123</v>
@@ -5774,41 +5205,38 @@
       <c r="M62" s="11">
         <v>50</v>
       </c>
-      <c r="N62" s="16"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
+      <c r="O62" s="4"/>
       <c r="R62" s="12">
         <v>2</v>
       </c>
       <c r="S62" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T62" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T62" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U62" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="V62" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W62" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="V62" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="W62" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23">
-      <c r="A63" s="11" t="s">
+      <c r="B63" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="C63" s="12">
         <v>2</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E63" s="12">
         <v>331</v>
@@ -5837,41 +5265,37 @@
       <c r="M63" s="11">
         <v>60</v>
       </c>
-      <c r="N63" s="16"/>
-      <c r="O63" s="16"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
       <c r="R63" s="12">
         <v>2</v>
       </c>
       <c r="S63" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T63" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T63" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U63" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="V63" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W63" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="V63" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="W63" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23">
-      <c r="A64" s="11" t="s">
+      <c r="B64" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="C64" s="12">
         <v>3</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E64" s="12">
         <v>746</v>
@@ -5900,41 +5324,37 @@
       <c r="M64" s="11">
         <v>70</v>
       </c>
-      <c r="N64" s="16"/>
-      <c r="O64" s="16"/>
-      <c r="P64" s="17"/>
-      <c r="Q64" s="17"/>
       <c r="R64" s="12">
         <v>3</v>
       </c>
       <c r="S64" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T64" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T64" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U64" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="V64" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W64" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A65" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="V64" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="W64" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23">
-      <c r="A65" s="11" t="s">
+      <c r="B65" s="11" t="s">
         <v>259</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="C65" s="12">
         <v>4</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E65" s="12">
         <v>2987</v>
@@ -5963,41 +5383,37 @@
       <c r="M65" s="11">
         <v>80</v>
       </c>
-      <c r="N65" s="16"/>
-      <c r="O65" s="16"/>
-      <c r="P65" s="17"/>
-      <c r="Q65" s="17"/>
       <c r="R65" s="12">
         <v>3</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T65" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T65" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U65" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="V65" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W65" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A66" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="V65" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="W65" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23">
-      <c r="A66" s="11" t="s">
+      <c r="B66" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="C66" s="12">
         <v>5</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E66" s="12">
         <v>6470</v>
@@ -6026,41 +5442,37 @@
       <c r="M66" s="11">
         <v>90</v>
       </c>
-      <c r="N66" s="16"/>
-      <c r="O66" s="16"/>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
       <c r="R66" s="12">
         <v>4</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T66" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T66" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U66" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="V66" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W66" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="V66" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="W66" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23">
-      <c r="A67" s="11" t="s">
+      <c r="B67" s="11" t="s">
         <v>266</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>267</v>
       </c>
       <c r="C67" s="12">
         <v>6</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E67" s="12">
         <v>19907</v>
@@ -6089,41 +5501,37 @@
       <c r="M67" s="11">
         <v>100</v>
       </c>
-      <c r="N67" s="16"/>
-      <c r="O67" s="16"/>
-      <c r="P67" s="17"/>
-      <c r="Q67" s="17"/>
       <c r="R67" s="12">
         <v>4</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T67" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T67" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U67" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="V67" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W67" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A68" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="V67" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="W67" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23">
-      <c r="A68" s="11" t="s">
+      <c r="B68" s="11" t="s">
         <v>269</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>270</v>
       </c>
       <c r="C68" s="12">
         <v>7</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E68" s="12">
         <v>43130</v>
@@ -6152,33 +5560,88 @@
       <c r="M68" s="11">
         <v>110</v>
       </c>
-      <c r="N68" s="16"/>
-      <c r="O68" s="16"/>
-      <c r="P68" s="17"/>
-      <c r="Q68" s="17"/>
       <c r="R68" s="12">
         <v>5</v>
       </c>
       <c r="S68" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="T68" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="T68" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="U68" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="V68" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W68" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A69" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C69" s="12">
+        <v>8</v>
+      </c>
+      <c r="D69" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="V68" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="W68" s="11" t="b">
+      <c r="E69" s="12">
+        <v>100000</v>
+      </c>
+      <c r="F69" s="4">
+        <v>1</v>
+      </c>
+      <c r="G69" s="12">
+        <v>10</v>
+      </c>
+      <c r="H69" s="4">
+        <v>1</v>
+      </c>
+      <c r="I69" s="4">
+        <v>3</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="K69" s="12">
+        <v>280</v>
+      </c>
+      <c r="L69" s="12">
+        <v>230</v>
+      </c>
+      <c r="M69" s="11">
+        <v>250</v>
+      </c>
+      <c r="R69" s="4">
+        <v>7</v>
+      </c>
+      <c r="S69" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="T69" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="U69" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="V69" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="W69" s="11" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>